--- a/figures/FMNIST/tables/unlearning_rate/noise_fashion_v1_delta_fashion_v2/results.xlsx
+++ b/figures/FMNIST/tables/unlearning_rate/noise_fashion_v1_delta_fashion_v2/results.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maciek\Documents\GitHub\MUNDataStream\figures\FMNIST\tables\unlearning_rate\noise_fashion_v1_delta_fashion_v2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9DD472-2FFC-4BD4-95A0-71F070D953A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="4650" yWindow="5730" windowWidth="28800" windowHeight="15885" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="accuracy" sheetId="1" r:id="rId1"/>
     <sheet name="recovery_time" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>unlearning_rate</t>
   </si>
@@ -35,17 +41,14 @@
     <t>accuracy_recovery_time</t>
   </si>
   <si>
-    <t>mean_memory</t>
-  </si>
-  <si>
     <t>mean_time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,17 +107,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office 2007–2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -152,7 +163,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office 2007–2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -186,6 +197,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -220,9 +232,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office 2007–2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,11 +408,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -413,116 +426,116 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.8613562559694364</v>
+        <v>0.86135625596943644</v>
       </c>
       <c r="C2">
         <v>0.8224808429118774</v>
       </c>
       <c r="D2">
-        <v>0.9000095238095238</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>0.90000952380952381</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.03</v>
       </c>
       <c r="B3">
-        <v>0.8583906399235913</v>
+        <v>0.85839063992359133</v>
       </c>
       <c r="C3">
-        <v>0.8175383141762452</v>
+        <v>0.81753831417624523</v>
       </c>
       <c r="D3">
-        <v>0.8990095238095238</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>0.89900952380952381</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.05</v>
       </c>
       <c r="B4">
-        <v>0.8573018147086915</v>
+        <v>0.85730181470869149</v>
       </c>
       <c r="C4">
-        <v>0.8207950191570882</v>
+        <v>0.82079501915708819</v>
       </c>
       <c r="D4">
-        <v>0.8935999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>0.89359999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.1</v>
       </c>
       <c r="B5">
-        <v>0.8583190066857689</v>
+        <v>0.85831900668576888</v>
       </c>
       <c r="C5">
-        <v>0.8174233716475097</v>
+        <v>0.81742337164750967</v>
       </c>
       <c r="D5">
-        <v>0.8989809523809523</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>0.89898095238095233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.2</v>
       </c>
       <c r="B6">
-        <v>0.8558882521489971</v>
+        <v>0.85588825214899711</v>
       </c>
       <c r="C6">
-        <v>0.8202394636015327</v>
+        <v>0.82023946360153266</v>
       </c>
       <c r="D6">
-        <v>0.8913333333333333</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>0.89133333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.3</v>
       </c>
       <c r="B7">
-        <v>0.8301384909264565</v>
+        <v>0.83013849092645653</v>
       </c>
       <c r="C7">
-        <v>0.8217624521072796</v>
+        <v>0.82176245210727961</v>
       </c>
       <c r="D7">
-        <v>0.8384666666666667</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>0.83846666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8">
-        <v>0.8545988538681948</v>
+        <v>0.85459885386819479</v>
       </c>
       <c r="C8">
-        <v>0.8114942528735632</v>
+        <v>0.81149425287356325</v>
       </c>
       <c r="D8">
-        <v>0.8974571428571428</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>0.89745714285714284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
       <c r="B9">
-        <v>0.8691404011461318</v>
+        <v>0.86914040114613178</v>
       </c>
       <c r="C9">
-        <v>0.8349808429118775</v>
+        <v>0.83498084291187746</v>
       </c>
       <c r="D9">
-        <v>0.9031047619047619</v>
+        <v>0.90310476190476185</v>
       </c>
     </row>
   </sheetData>
@@ -531,11 +544,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -545,11 +558,8 @@
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.01</v>
       </c>
@@ -557,13 +567,10 @@
         <v>15.33333333333333</v>
       </c>
       <c r="C2">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D2">
-        <v>3.622840367135624</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>3.6228403671356242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.03</v>
       </c>
@@ -571,13 +578,10 @@
         <v>11.33333333333333</v>
       </c>
       <c r="C3">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D3">
-        <v>3.633167400702959</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>3.6331674007029591</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.05</v>
       </c>
@@ -585,13 +589,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D4">
         <v>3.629364886501437</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.1</v>
       </c>
@@ -599,13 +600,10 @@
         <v>10.33333333333333</v>
       </c>
       <c r="C5">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D5">
-        <v>3.59517491436103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>3.5951749143610301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.2</v>
       </c>
@@ -613,13 +611,10 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D6">
         <v>3.596917230154725</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.3</v>
       </c>
@@ -627,13 +622,10 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D7">
         <v>3.631464565500476</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -641,13 +633,10 @@
         <v>13.33333333333333</v>
       </c>
       <c r="C8">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D8">
         <v>2.180985720647564</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -655,10 +644,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="C9">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D9">
-        <v>6.271977036589309</v>
+        <v>6.2719770365893091</v>
       </c>
     </row>
   </sheetData>
